--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_2_15.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_2_15.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>576356.8618530994</v>
+        <v>579642.9800400217</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446351659</v>
+        <v>925399.3994514376</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422524</v>
+        <v>18327015.93006068</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5477073.903928688</v>
+        <v>5477185.456223348</v>
       </c>
     </row>
     <row r="11">
@@ -694,25 +694,25 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W2" t="n">
-        <v>102.2970636939287</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>146.1378473354543</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D3" t="n">
         <v>147.4450655646388</v>
@@ -749,7 +749,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -822,16 +822,16 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="I4" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -931,19 +931,19 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S5" t="n">
-        <v>19.70106086546267</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V5" t="n">
-        <v>241</v>
+        <v>112.3289263072337</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -965,10 +965,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D6" t="n">
-        <v>20.99531631735417</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
         <v>157.6450804554009</v>
@@ -1010,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>93.35918011667277</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="K7" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1129,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.809496073036132</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I8" t="n">
         <v>210.4758895704059</v>
@@ -1168,16 +1168,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>142.8118733380676</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1205,25 +1205,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1247,22 +1247,22 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>63.85130908303156</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.833957768458675</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1299,13 +1299,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,13 +1320,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1366,19 +1366,19 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1.809496073036132</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H11" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I11" t="n">
-        <v>112.2877629084735</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1405,13 +1405,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1442,22 +1442,22 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>145.0692123933839</v>
+        <v>124.3469240739945</v>
       </c>
       <c r="G12" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>75.92891916688478</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1560,10 +1560,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1606,16 +1606,16 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>82.93709327389956</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1645,16 +1645,16 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>102.3382270926889</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1676,22 +1676,22 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>146.1932996118735</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -1721,19 +1721,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>10.58553395309683</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1834,10 +1834,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1882,22 +1882,22 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>112.3289263072337</v>
       </c>
       <c r="W17" t="n">
-        <v>62.40368205885025</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>123.7367568936677</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1958,28 +1958,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.580549094716531</v>
       </c>
       <c r="X18" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2049,10 +2049,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W19" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2071,19 +2071,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>40.46369348972969</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2116,16 +2116,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>190.3453970742849</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>131.7659851933074</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2198,25 +2198,25 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>54.78790762601773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2283,13 +2283,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2311,16 +2311,16 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2356,22 +2356,22 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>190.3328114308427</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>190.3453970742849</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>117.5614415552192</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>182.7004482653351</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2548,16 +2548,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>190.3328114308427</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>241</v>
+        <v>190.3453970742848</v>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2672,25 +2672,25 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>191.2090207741688</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>29.79900896488263</v>
       </c>
     </row>
     <row r="28">
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.252730413812432</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2830,22 +2830,22 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2858,22 +2858,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>126.3031379239677</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>11.53180811788352</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2918,10 +2918,10 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -2943,58 +2943,58 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3022,16 +3022,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>212.2728000000362</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F32" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G32" t="n">
-        <v>241</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="33">
@@ -3098,28 +3098,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>54.27206683872637</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>64.20082132715153</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3225,19 +3225,19 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3268,16 +3268,16 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>52.42556848774763</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3310,19 +3310,19 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>190.3328114308427</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
@@ -3353,10 +3353,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>67.92775320576783</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>127.0497292502256</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>200.3235106453875</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3508,13 +3508,13 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3535,10 +3535,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3550,16 +3550,16 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>241</v>
+        <v>52.42556848774763</v>
       </c>
       <c r="Y38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>145.3912560091964</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>77.92691371295918</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1.809496073036188</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3784,19 +3784,19 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>202.2821007854552</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="42">
@@ -3806,16 +3806,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3824,13 +3824,13 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>21.77931370777366</v>
       </c>
       <c r="I42" t="n">
-        <v>29.75784556612239</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3860,19 +3860,19 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3970,16 +3970,16 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>84.41978777916125</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4012,10 +4012,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -4024,16 +4024,16 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>202.2821007855562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4046,22 +4046,22 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>152.2207240410305</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E45" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>66.3257810793199</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4179,19 +4179,19 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R2" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S2" t="n">
-        <v>591.3940537960203</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T2" t="n">
-        <v>366.0447108019482</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U2" t="n">
-        <v>122.6103673676048</v>
+        <v>710.516763498309</v>
       </c>
       <c r="V2" t="n">
-        <v>122.6103673676048</v>
+        <v>467.067986854209</v>
       </c>
       <c r="W2" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="X2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C3" t="n">
-        <v>816.3860127924704</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D3" t="n">
-        <v>667.4516031312191</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E3" t="n">
-        <v>508.2141481257637</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F3" t="n">
-        <v>361.6795901526487</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G3" t="n">
-        <v>222.9487647352642</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H3" t="n">
-        <v>109.5796291428435</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I3" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L3" t="n">
-        <v>19.28</v>
+        <v>234.810827406191</v>
       </c>
       <c r="M3" t="n">
-        <v>234.7819638733197</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N3" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O3" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I4" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J4" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S5" t="n">
-        <v>944.0999385197347</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T5" t="n">
-        <v>718.7505955256626</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="U5" t="n">
-        <v>475.3162520913191</v>
+        <v>132.7447050367114</v>
       </c>
       <c r="V5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y5" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C6" t="n">
-        <v>689.4131260035546</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D6" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E6" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F6" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G6" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H6" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I6" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L6" t="n">
-        <v>144.6375600578374</v>
+        <v>234.810827406191</v>
       </c>
       <c r="M6" t="n">
-        <v>304.1765223866491</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N6" t="n">
-        <v>542.7665223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="O6" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P6" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="C7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="D7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="E7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="F7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="G7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="H7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="I7" t="n">
-        <v>136.0766383258138</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="J7" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="S7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="T7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="U7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="V7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="W7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="X7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="Y7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>231.8819086569757</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C8" t="n">
-        <v>231.8819086569757</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D8" t="n">
-        <v>231.8819086569757</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E8" t="n">
-        <v>231.8819086569757</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="F8" t="n">
-        <v>231.8819086569757</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="G8" t="n">
-        <v>231.8819086569757</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="H8" t="n">
-        <v>231.8819086569757</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R8" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S8" t="n">
-        <v>601.4856691642474</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T8" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U8" t="n">
-        <v>231.8819086569757</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V8" t="n">
-        <v>231.8819086569757</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W8" t="n">
-        <v>231.8819086569757</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X8" t="n">
-        <v>231.8819086569757</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y8" t="n">
-        <v>231.8819086569757</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>726.0863836496269</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C9" t="n">
-        <v>726.0863836496269</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D9" t="n">
-        <v>577.1519739883756</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E9" t="n">
-        <v>417.9145189829202</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F9" t="n">
-        <v>271.3799610098052</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G9" t="n">
-        <v>132.6491355924207</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H9" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I9" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L9" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M9" t="n">
-        <v>249.2431058683491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N9" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O9" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P9" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>899.503728198958</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S9" t="n">
-        <v>726.0863836496269</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T9" t="n">
-        <v>726.0863836496269</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U9" t="n">
-        <v>726.0863836496269</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V9" t="n">
-        <v>726.0863836496269</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W9" t="n">
-        <v>726.0863836496269</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="X9" t="n">
-        <v>726.0863836496269</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="Y9" t="n">
-        <v>726.0863836496269</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I10" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q10" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E11" t="n">
-        <v>376.1363261701753</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="F11" t="n">
-        <v>376.1363261701753</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="G11" t="n">
-        <v>376.1363261701753</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="H11" t="n">
-        <v>132.7019827358318</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R11" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S11" t="n">
-        <v>601.4856691642474</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>689.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="C12" t="n">
-        <v>689.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="D12" t="n">
-        <v>540.4787163423033</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="E12" t="n">
-        <v>381.2412613368478</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="F12" t="n">
-        <v>234.7067033637328</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G12" t="n">
-        <v>95.97587794634828</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H12" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L12" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M12" t="n">
-        <v>234.7819638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N12" t="n">
-        <v>473.3719638733197</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O12" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P12" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S12" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T12" t="n">
-        <v>689.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U12" t="n">
-        <v>689.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="V12" t="n">
-        <v>689.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="W12" t="n">
-        <v>689.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="X12" t="n">
-        <v>689.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="Y12" t="n">
-        <v>689.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I13" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q13" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>802.5254372164702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C14" t="n">
-        <v>802.5254372164702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D14" t="n">
-        <v>802.5254372164702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E14" t="n">
-        <v>802.5254372164702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F14" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G14" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H14" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R14" t="n">
-        <v>802.5254372164702</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S14" t="n">
-        <v>802.5254372164702</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T14" t="n">
-        <v>802.5254372164702</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U14" t="n">
-        <v>802.5254372164702</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="V14" t="n">
-        <v>802.5254372164702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W14" t="n">
-        <v>802.5254372164702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X14" t="n">
-        <v>802.5254372164702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y14" t="n">
-        <v>802.5254372164702</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>248.310454560228</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C15" t="n">
-        <v>248.310454560228</v>
+        <v>816.3871559026832</v>
       </c>
       <c r="D15" t="n">
-        <v>248.310454560228</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="E15" t="n">
-        <v>248.310454560228</v>
+        <v>508.2152912359765</v>
       </c>
       <c r="F15" t="n">
-        <v>248.310454560228</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G15" t="n">
-        <v>109.5796291428435</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H15" t="n">
-        <v>109.5796291428435</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L15" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M15" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N15" t="n">
-        <v>725.41</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O15" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P15" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T15" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U15" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V15" t="n">
-        <v>248.310454560228</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W15" t="n">
-        <v>248.310454560228</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X15" t="n">
-        <v>248.310454560228</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y15" t="n">
-        <v>248.310454560228</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I16" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C17" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R17" t="n">
-        <v>812.6170525846973</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S17" t="n">
-        <v>812.6170525846973</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T17" t="n">
-        <v>812.6170525846973</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="U17" t="n">
-        <v>812.6170525846973</v>
+        <v>132.7447050367114</v>
       </c>
       <c r="V17" t="n">
-        <v>812.6170525846973</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W17" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X17" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y17" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>145.0207557777026</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L18" t="n">
-        <v>249.2431058683491</v>
+        <v>178.8501590306595</v>
       </c>
       <c r="M18" t="n">
-        <v>487.8331058683492</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N18" t="n">
-        <v>726.4231058683491</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O18" t="n">
-        <v>726.4231058683491</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P18" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S18" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T18" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U18" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V18" t="n">
-        <v>728.8478917682573</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W18" t="n">
-        <v>728.8478917682573</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X18" t="n">
-        <v>520.9963915627245</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y18" t="n">
-        <v>313.2360927977706</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>315.6567503478204</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="C20" t="n">
-        <v>72.22240691347699</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="D20" t="n">
-        <v>72.22240691347699</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="E20" t="n">
-        <v>72.22240691347699</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="F20" t="n">
-        <v>72.22240691347699</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G20" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H20" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I20" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935105359</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951945</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580987</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565338</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.3399447079861</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964.0000000000371</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.90838463181</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>802.5254372165073</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S20" t="n">
-        <v>802.5254372165073</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T20" t="n">
-        <v>802.5254372165073</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="U20" t="n">
-        <v>802.5254372165073</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="V20" t="n">
-        <v>802.5254372165073</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="W20" t="n">
-        <v>802.5254372165073</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="X20" t="n">
-        <v>559.0910937821639</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="Y20" t="n">
-        <v>315.6567503478204</v>
+        <v>518.2486856454962</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.03413265278571</v>
+        <v>152.3780978509273</v>
       </c>
       <c r="C21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>304.1765223866491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T21" t="n">
-        <v>761.813405358766</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U21" t="n">
-        <v>761.813405358766</v>
+        <v>360.2295980564601</v>
       </c>
       <c r="V21" t="n">
-        <v>526.6612971270233</v>
+        <v>360.2295980564601</v>
       </c>
       <c r="W21" t="n">
-        <v>283.2269536926799</v>
+        <v>360.2295980564601</v>
       </c>
       <c r="X21" t="n">
-        <v>75.37545348714707</v>
+        <v>152.3780978509273</v>
       </c>
       <c r="Y21" t="n">
-        <v>20.03413265278571</v>
+        <v>152.3780978509273</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>274.7843326814268</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="C23" t="n">
-        <v>274.7843326814268</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="D23" t="n">
-        <v>31.34998924708335</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="E23" t="n">
-        <v>31.34998924708335</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="F23" t="n">
-        <v>31.34998924708335</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G23" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H23" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I23" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S23" t="n">
-        <v>761.6530195501136</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T23" t="n">
-        <v>761.6530195501136</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U23" t="n">
-        <v>518.2186761157702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V23" t="n">
-        <v>274.7843326814268</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W23" t="n">
-        <v>274.7843326814268</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X23" t="n">
-        <v>274.7843326814268</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="Y23" t="n">
-        <v>274.7843326814268</v>
+        <v>761.6974622895962</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>194.4871619339127</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>234.7819638733197</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M24" t="n">
-        <v>473.3719638733197</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T24" t="n">
-        <v>845.2510691361422</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U24" t="n">
-        <v>845.2510691361422</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V24" t="n">
-        <v>610.0989609043995</v>
+        <v>678.3417187247995</v>
       </c>
       <c r="W24" t="n">
-        <v>610.0989609043995</v>
+        <v>434.8929420806995</v>
       </c>
       <c r="X24" t="n">
-        <v>402.2474606988666</v>
+        <v>227.0414418751666</v>
       </c>
       <c r="Y24" t="n">
-        <v>194.4871619339127</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>953.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="C26" t="n">
-        <v>953.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="D26" t="n">
-        <v>761.6530195501136</v>
+        <v>710.516763498309</v>
       </c>
       <c r="E26" t="n">
-        <v>518.2186761157702</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="F26" t="n">
-        <v>274.7843326814268</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G26" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H26" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I26" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y26" t="n">
-        <v>953.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>487.8331058683492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N27" t="n">
-        <v>725.41</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O27" t="n">
-        <v>964</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>588.3960608094349</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>588.3960608094349</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V27" t="n">
-        <v>395.2556357850219</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W27" t="n">
-        <v>395.2556357850219</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X27" t="n">
-        <v>395.2556357850219</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y27" t="n">
-        <v>187.495337020068</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935105573</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450952159</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.29047235812</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.1449945653594</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3399447080075</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>752.8686165796086</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>752.8686165796086</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U29" t="n">
-        <v>752.8686165796086</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V29" t="n">
-        <v>752.8686165796086</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W29" t="n">
-        <v>509.4342731452651</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X29" t="n">
-        <v>509.4342731452651</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y29" t="n">
-        <v>509.4342731452651</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>795.7846629799319</v>
+        <v>384.2867411876791</v>
       </c>
       <c r="C30" t="n">
-        <v>668.2057357840049</v>
+        <v>384.2867411876791</v>
       </c>
       <c r="D30" t="n">
-        <v>668.2057357840049</v>
+        <v>235.3523315264278</v>
       </c>
       <c r="E30" t="n">
-        <v>508.9682807785495</v>
+        <v>235.3523315264278</v>
       </c>
       <c r="F30" t="n">
-        <v>362.4337228054344</v>
+        <v>235.3523315264278</v>
       </c>
       <c r="G30" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H30" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M30" t="n">
-        <v>487.8331058683492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V30" t="n">
-        <v>964</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="W30" t="n">
-        <v>964</v>
+        <v>384.2867411876791</v>
       </c>
       <c r="X30" t="n">
-        <v>964</v>
+        <v>384.2867411876791</v>
       </c>
       <c r="Y30" t="n">
-        <v>964</v>
+        <v>384.2867411876791</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>720.5656565656932</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C32" t="n">
-        <v>720.5656565656932</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D32" t="n">
-        <v>506.1486868686869</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E32" t="n">
-        <v>506.1486868686869</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="F32" t="n">
-        <v>262.7143434343434</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2389935105355</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3148450951941</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.2904723580982</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.1449945653376</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.3399447079856</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964.0000000000366</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>964.0000000000366</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>964.0000000000366</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>964.0000000000366</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>964.0000000000366</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U32" t="n">
-        <v>964.0000000000366</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V32" t="n">
-        <v>964.0000000000366</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W32" t="n">
-        <v>964.0000000000366</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X32" t="n">
-        <v>720.5656565656932</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y32" t="n">
-        <v>720.5656565656932</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>730.9353485080618</v>
+        <v>622.424473941237</v>
       </c>
       <c r="C33" t="n">
-        <v>556.4823192269348</v>
+        <v>567.60420440717</v>
       </c>
       <c r="D33" t="n">
-        <v>407.5479095656835</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="E33" t="n">
-        <v>248.310454560228</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="F33" t="n">
-        <v>248.310454560228</v>
+        <v>272.1352367728036</v>
       </c>
       <c r="G33" t="n">
-        <v>109.5796291428435</v>
+        <v>133.4044113554191</v>
       </c>
       <c r="H33" t="n">
-        <v>109.5796291428435</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I33" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M33" t="n">
-        <v>417.4254414866706</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N33" t="n">
-        <v>656.0154414866706</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O33" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P33" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T33" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U33" t="n">
-        <v>899.1506855281298</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="V33" t="n">
-        <v>899.1506855281298</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="W33" t="n">
-        <v>899.1506855281298</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="X33" t="n">
-        <v>899.1506855281298</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="Y33" t="n">
-        <v>899.1506855281298</v>
+        <v>790.6398109613051</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>274.7843326814268</v>
+        <v>315.6850394389064</v>
       </c>
       <c r="C35" t="n">
-        <v>274.7843326814268</v>
+        <v>72.23626279480629</v>
       </c>
       <c r="D35" t="n">
-        <v>274.7843326814268</v>
+        <v>72.23626279480629</v>
       </c>
       <c r="E35" t="n">
-        <v>274.7843326814268</v>
+        <v>72.23626279480629</v>
       </c>
       <c r="F35" t="n">
-        <v>274.7843326814268</v>
+        <v>72.23626279480629</v>
       </c>
       <c r="G35" t="n">
-        <v>31.34998924708335</v>
+        <v>72.23626279480629</v>
       </c>
       <c r="H35" t="n">
-        <v>31.34998924708335</v>
+        <v>72.23626279480629</v>
       </c>
       <c r="I35" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R35" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S35" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T35" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U35" t="n">
-        <v>953.9083846317729</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="V35" t="n">
-        <v>953.9083846317729</v>
+        <v>315.6850394389064</v>
       </c>
       <c r="W35" t="n">
-        <v>953.9083846317729</v>
+        <v>315.6850394389064</v>
       </c>
       <c r="X35" t="n">
-        <v>761.6530195501136</v>
+        <v>315.6850394389064</v>
       </c>
       <c r="Y35" t="n">
-        <v>518.2186761157702</v>
+        <v>315.6850394389064</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>667.4516031312191</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="C36" t="n">
-        <v>667.4516031312191</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="D36" t="n">
-        <v>667.4516031312191</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="E36" t="n">
-        <v>508.2141481257637</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="F36" t="n">
-        <v>361.6795901526487</v>
+        <v>340.7491288998418</v>
       </c>
       <c r="G36" t="n">
-        <v>222.9487647352642</v>
+        <v>202.0183034824573</v>
       </c>
       <c r="H36" t="n">
-        <v>109.5796291428435</v>
+        <v>88.64916789003665</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M36" t="n">
-        <v>417.4254414866706</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N36" t="n">
-        <v>656.0154414866706</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O36" t="n">
-        <v>894.6054414866707</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P36" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S36" t="n">
-        <v>835.6669401512872</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T36" t="n">
-        <v>835.6669401512872</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U36" t="n">
-        <v>835.6669401512872</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="V36" t="n">
-        <v>835.6669401512872</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="W36" t="n">
-        <v>835.6669401512872</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="X36" t="n">
-        <v>835.6669401512872</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="Y36" t="n">
-        <v>835.6669401512872</v>
+        <v>487.2836868729568</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>233.6969696969697</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C38" t="n">
-        <v>233.6969696969697</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D38" t="n">
-        <v>233.6969696969697</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E38" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F38" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G38" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H38" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S38" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T38" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U38" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="V38" t="n">
-        <v>964</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="W38" t="n">
-        <v>964</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="X38" t="n">
-        <v>720.5656565656566</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y38" t="n">
-        <v>477.1313131313132</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>817.1401454452562</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="C39" t="n">
-        <v>817.1401454452562</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="D39" t="n">
-        <v>668.2057357840049</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="E39" t="n">
-        <v>508.9682807785495</v>
+        <v>97.99519736572705</v>
       </c>
       <c r="F39" t="n">
-        <v>362.4337228054344</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>19.28</v>
+        <v>74.24228005117135</v>
       </c>
       <c r="L39" t="n">
-        <v>234.7819638733197</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M39" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N39" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O39" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P39" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U39" t="n">
-        <v>964</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V39" t="n">
-        <v>964</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W39" t="n">
-        <v>964</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X39" t="n">
-        <v>964</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="Y39" t="n">
-        <v>964</v>
+        <v>257.2326523711826</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>262.7143434343434</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="C41" t="n">
-        <v>262.7143434343434</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="D41" t="n">
-        <v>262.7143434343434</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="E41" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="F41" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="G41" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="H41" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U41" t="n">
-        <v>953.9083846317729</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V41" t="n">
-        <v>953.9083846317729</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="W41" t="n">
-        <v>710.4740411974295</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="X41" t="n">
-        <v>467.0396977630861</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y41" t="n">
-        <v>262.7143434343434</v>
+        <v>233.7108255783361</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>49.33842986477009</v>
+        <v>350.2064472052342</v>
       </c>
       <c r="C42" t="n">
-        <v>49.33842986477009</v>
+        <v>350.2064472052342</v>
       </c>
       <c r="D42" t="n">
-        <v>49.33842986477009</v>
+        <v>201.2720375439829</v>
       </c>
       <c r="E42" t="n">
-        <v>49.33842986477009</v>
+        <v>42.03458253852739</v>
       </c>
       <c r="F42" t="n">
-        <v>49.33842986477009</v>
+        <v>42.03458253852739</v>
       </c>
       <c r="G42" t="n">
-        <v>49.33842986477009</v>
+        <v>42.03458253852739</v>
       </c>
       <c r="H42" t="n">
-        <v>49.33842986477009</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L42" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M42" t="n">
-        <v>234.7819638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N42" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O42" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P42" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T42" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U42" t="n">
-        <v>735.7763817363891</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V42" t="n">
-        <v>500.6242735046464</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W42" t="n">
-        <v>257.1899300703029</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="X42" t="n">
-        <v>49.33842986477009</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="Y42" t="n">
-        <v>49.33842986477009</v>
+        <v>518.4217842253022</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>506.1486868686869</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="C44" t="n">
-        <v>506.1486868686869</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="D44" t="n">
-        <v>262.7143434343434</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="E44" t="n">
-        <v>19.28</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="F44" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.238993510601</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3148450952596</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.2904723581637</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.1449945654031</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.3399447080511</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964.0000000001021</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.908384631875</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R44" t="n">
-        <v>953.908384631875</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S44" t="n">
-        <v>953.908384631875</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T44" t="n">
-        <v>953.908384631875</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="U44" t="n">
-        <v>953.908384631875</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="V44" t="n">
-        <v>953.908384631875</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="W44" t="n">
-        <v>710.4740411975316</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="X44" t="n">
-        <v>710.4740411975316</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="Y44" t="n">
-        <v>506.1486868686869</v>
+        <v>348.0024326625565</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.2440188867995</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C45" t="n">
-        <v>384.2440188867995</v>
+        <v>566.8500717543842</v>
       </c>
       <c r="D45" t="n">
-        <v>384.2440188867995</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="E45" t="n">
-        <v>225.006563881344</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="F45" t="n">
-        <v>158.0108254173845</v>
+        <v>271.3811041200179</v>
       </c>
       <c r="G45" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L45" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M45" t="n">
-        <v>613.1906659261865</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N45" t="n">
-        <v>656.0154414866706</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O45" t="n">
-        <v>894.6054414866707</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P45" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S45" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T45" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U45" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V45" t="n">
-        <v>627.6783623211429</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W45" t="n">
-        <v>384.2440188867995</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X45" t="n">
-        <v>384.2440188867995</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y45" t="n">
-        <v>384.2440188867995</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
   </sheetData>
@@ -7971,7 +7971,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O2" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P2" t="n">
         <v>321.7987081714826</v>
@@ -8041,16 +8041,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L3" t="n">
-        <v>138.5543797798742</v>
+        <v>356.2611315939937</v>
       </c>
       <c r="M3" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N3" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O3" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P3" t="n">
         <v>318.4627686399372</v>
@@ -8196,7 +8196,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L5" t="n">
         <v>417.6612145504504</v>
@@ -8278,22 +8278,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L6" t="n">
-        <v>138.5543797798742</v>
+        <v>229.6373335557741</v>
       </c>
       <c r="M6" t="n">
-        <v>303.2845009208181</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O6" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P6" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L8" t="n">
         <v>417.6612145504504</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L9" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M9" t="n">
-        <v>142.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N9" t="n">
-        <v>357.73449794694</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P9" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q9" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8670,7 +8670,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L11" t="n">
         <v>417.6612145504504</v>
@@ -8749,25 +8749,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M12" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N12" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O12" t="n">
-        <v>383.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P12" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8907,7 +8907,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L14" t="n">
         <v>417.6612145504504</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L15" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M15" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N15" t="n">
-        <v>371.3183728223746</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O15" t="n">
-        <v>383.5962444444444</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P15" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9144,7 +9144,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L17" t="n">
         <v>417.6612145504504</v>
@@ -9223,22 +9223,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L18" t="n">
-        <v>370.8403453034592</v>
+        <v>173.111405903722</v>
       </c>
       <c r="M18" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N18" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P18" t="n">
-        <v>303.8555545035439</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
         <v>210.0772877358491</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889562</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,13 +9466,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>197.6223334354527</v>
+        <v>197.6503338623806</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>229.6093331288462</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>382.6009056104135</v>
       </c>
       <c r="P24" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N27" t="n">
-        <v>371.3183728223746</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889778</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10177,16 +10177,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>186.8300115967677</v>
+        <v>371.3463732493024</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
         <v>139.9817740860215</v>
@@ -10329,7 +10329,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>324.0888343889558</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
@@ -10414,13 +10414,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>185.3913829730123</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>372.3417120833333</v>
+        <v>174.6270615612551</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>133.9744074143302</v>
@@ -10581,7 +10581,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10651,19 +10651,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>185.3913829730123</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N36" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,7 +10803,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>193.3577389147212</v>
       </c>
       <c r="L39" t="n">
-        <v>356.2331311670658</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N39" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11046,7 +11046,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>359.81278530921</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N42" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11277,7 +11277,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K44" t="n">
-        <v>324.0888343890219</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L44" t="n">
         <v>417.6612145504504</v>
@@ -11356,22 +11356,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
-        <v>383.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N45" t="n">
-        <v>174.5990611343274</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P45" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q45" t="n">
         <v>210.0772877358491</v>
@@ -22552,25 +22552,25 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V2" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W2" t="n">
-        <v>246.9439050234843</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X2" t="n">
-        <v>369.731100678469</v>
+        <v>167.4364142495718</v>
       </c>
       <c r="Y2" t="n">
         <v>386.2379386560536</v>
@@ -22586,7 +22586,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>26.57065165286144</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -22607,7 +22607,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -22680,16 +22680,16 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H4" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I4" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -22762,7 +22762,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
         <v>11.94928935461252</v>
@@ -22789,19 +22789,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>189.3190087207827</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V5" t="n">
-        <v>86.7522584701349</v>
+        <v>215.4233321629012</v>
       </c>
       <c r="W5" t="n">
         <v>349.240968717413</v>
@@ -22823,10 +22823,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D6" t="n">
-        <v>126.4497492472846</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -22868,10 +22868,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
         <v>200.1647286948216</v>
@@ -22920,13 +22920,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>46.33425578299912</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -22944,7 +22944,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>177.2933913771695</v>
@@ -22987,16 +22987,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E8" t="n">
-        <v>381.9303700722618</v>
+        <v>380.1208739992256</v>
       </c>
       <c r="F8" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G8" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -23026,16 +23026,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>108.5337795697689</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23063,25 +23063,25 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,22 +23105,22 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>36.30652506961157</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>251.6949831609196</v>
+        <v>247.8610253924609</v>
       </c>
       <c r="X9" t="n">
         <v>205.7729852034775</v>
@@ -23157,13 +23157,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,13 +23178,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23224,19 +23224,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E11" t="n">
-        <v>381.9303700722618</v>
+        <v>380.1208739992256</v>
       </c>
       <c r="F11" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G11" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H11" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I11" t="n">
-        <v>98.18812666193242</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23263,13 +23263,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
         <v>251.3456529078365</v>
@@ -23300,22 +23300,22 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>20.72228831938942</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>36.30652506961167</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -23348,7 +23348,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>225.9413820809748</v>
@@ -23394,13 +23394,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,10 +23418,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S13" t="n">
         <v>224.0165980369723</v>
@@ -23464,16 +23464,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>323.9389524678119</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23503,16 +23503,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V14" t="n">
-        <v>327.7522584701349</v>
+        <v>225.414031377446</v>
       </c>
       <c r="W14" t="n">
         <v>349.240968717413</v>
@@ -23534,22 +23534,22 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>172.7084989883157</v>
+        <v>26.51519937644221</v>
       </c>
       <c r="D15" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,19 +23579,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
-        <v>222.2150531963284</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W15" t="n">
         <v>251.6949831609196</v>
@@ -23631,13 +23631,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,13 +23652,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S16" t="n">
         <v>224.0165980369723</v>
@@ -23692,10 +23692,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C17" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D17" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E17" t="n">
         <v>381.9303700722618</v>
@@ -23740,22 +23740,22 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V17" t="n">
-        <v>327.7522584701349</v>
+        <v>215.4233321629012</v>
       </c>
       <c r="W17" t="n">
-        <v>286.8372866585628</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X17" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y17" t="n">
         <v>386.2379386560536</v>
@@ -23768,10 +23768,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C18" t="n">
-        <v>48.97174209464806</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
         <v>147.4450655646388</v>
@@ -23792,7 +23792,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>251.6949831609196</v>
+        <v>247.1144340662031</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="19">
@@ -23907,10 +23907,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W19" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
         <v>225.7096553890372</v>
@@ -23929,19 +23929,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F20" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>374.8390440254054</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>32.75045248984648</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -23992,10 +23992,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="21">
@@ -24008,7 +24008,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>40.94251379500832</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
@@ -24029,7 +24029,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24056,25 +24056,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>150.8947881512866</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24141,13 +24141,13 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
@@ -24169,16 +24169,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24214,22 +24214,22 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>18.68725815540262</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V23" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>179.3857036041842</v>
       </c>
       <c r="Y23" t="n">
         <v>386.2379386560536</v>
@@ -24245,7 +24245,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
@@ -24266,7 +24266,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24290,22 +24290,22 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>82.60328713960236</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>50.10013888409014</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -24375,7 +24375,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T25" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U25" t="n">
         <v>286.3190293564909</v>
@@ -24384,7 +24384,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X25" t="n">
         <v>225.7096553890372</v>
@@ -24406,16 +24406,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>164.3502301898402</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>140.9303700722618</v>
+        <v>191.584972997977</v>
       </c>
       <c r="F26" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H26" t="n">
         <v>339.4748021157671</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
@@ -24530,25 +24530,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>41.59156637525646</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>175.8836868124217</v>
       </c>
     </row>
     <row r="28">
@@ -24561,7 +24561,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C28" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325981</v>
       </c>
       <c r="D28" t="n">
         <v>148.6154730182124</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24637,16 +24637,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>379.4811112496681</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
         <v>406.8760457417114</v>
@@ -24688,22 +24688,22 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U29" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
         <v>386.2379386560536</v>
@@ -24716,22 +24716,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>46.405361064348</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>125.8117090453271</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
@@ -24776,10 +24776,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
@@ -24801,7 +24801,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D31" t="n">
-        <v>15.42850543284433</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E31" t="n">
         <v>146.4339626465692</v>
@@ -24852,7 +24852,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24880,16 +24880,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>142.4102416206468</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F32" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G32" t="n">
-        <v>174.302737515135</v>
+        <v>203.0173518716929</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24940,10 +24940,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="33">
@@ -24956,28 +24956,28 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>118.4364321495894</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25004,13 +25004,13 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>161.7405607538233</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25083,7 +25083,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
         <v>227.9455894282815</v>
@@ -25095,7 +25095,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25126,16 +25126,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
-        <v>210.4758895704059</v>
+        <v>158.0503210826583</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25159,7 +25159,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
@@ -25168,19 +25168,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V35" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>179.3982892476263</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
         <v>172.7084989883157</v>
@@ -25199,7 +25199,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -25211,10 +25211,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>21.46887964564725</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25238,13 +25238,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>44.63344185361218</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
@@ -25272,7 +25272,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C37" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325981</v>
       </c>
       <c r="D37" t="n">
         <v>148.6154730182124</v>
@@ -25332,7 +25332,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
         <v>225.7096553890372</v>
@@ -25348,7 +25348,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
@@ -25357,7 +25357,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>181.6068594268743</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F38" t="n">
         <v>406.8760457417114</v>
@@ -25366,13 +25366,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25393,10 +25393,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>209.0200695862453</v>
@@ -25408,16 +25408,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>128.731100678469</v>
+        <v>317.3055321907214</v>
       </c>
       <c r="Y38" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25427,31 +25427,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>21.14192764067096</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>67.1422986804247</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25484,13 +25484,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
@@ -25566,10 +25566,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W40" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>380.9243455904444</v>
       </c>
       <c r="C41" t="n">
         <v>365.2728917710076</v>
@@ -25594,7 +25594,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
@@ -25606,7 +25606,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25642,19 +25642,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V41" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W41" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>183.9558378705983</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="42">
@@ -25664,16 +25664,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
@@ -25682,13 +25682,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>90.45613052872281</v>
       </c>
       <c r="I42" t="n">
-        <v>59.63878728529269</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25718,19 +25718,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -25764,7 +25764,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I43" t="n">
-        <v>155.4504749272583</v>
+        <v>22.26350734189026</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -25806,7 +25806,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X43" t="n">
         <v>225.7096553890372</v>
@@ -25828,16 +25828,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D44" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E44" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F44" t="n">
-        <v>406.8760457417114</v>
+        <v>322.4562579625502</v>
       </c>
       <c r="G44" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H44" t="n">
         <v>339.4748021157671</v>
@@ -25870,10 +25870,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>223.0958495641314</v>
@@ -25882,16 +25882,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W44" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X44" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y44" t="n">
-        <v>183.9558378704973</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="45">
@@ -25904,22 +25904,22 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C45" t="n">
-        <v>172.7084989883157</v>
+        <v>20.48777494728526</v>
       </c>
       <c r="D45" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F45" t="n">
-        <v>78.74343131406398</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>89.39663285141508</v>
@@ -25949,7 +25949,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S45" t="n">
         <v>171.6831711038378</v>
@@ -25961,10 +25961,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X45" t="n">
         <v>205.7729852034775</v>
@@ -26037,7 +26037,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26049,7 +26049,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y46" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
   </sheetData>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>473667.3593581602</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>473667.3593581602</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>473667.3593581601</v>
+        <v>473677.0066044413</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>473667.3593581601</v>
+        <v>473677.0066044413</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>473667.3593581601</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>473667.3593581603</v>
+        <v>473677.006604441</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>473667.3593581644</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>473667.3593581603</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>473667.3593581602</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>473667.3593581668</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>473667.3593581643</v>
+        <v>473677.0066044413</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>473667.3593581603</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>473667.3593581603</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>473667.3593581602</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>473667.3593581716</v>
+        <v>473677.0066044412</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="C2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="D2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="E2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="F2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="G2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="H2" t="n">
-        <v>124617.9674568543</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="I2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="J2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="K2" t="n">
-        <v>124617.9674568549</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="L2" t="n">
-        <v>124617.9674568542</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="M2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="N2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="O2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="P2" t="n">
-        <v>124617.9674568561</v>
+        <v>124620.5043984993</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910623</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="C4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="D4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="E4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="F4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="G4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="H4" t="n">
-        <v>16914.33416026194</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="I4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="J4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="K4" t="n">
-        <v>16914.33416026203</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="L4" t="n">
-        <v>16914.33416026194</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="M4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="N4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="O4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="P4" t="n">
-        <v>16914.33416026221</v>
+        <v>16522.45939543529</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-21341.40970340863</v>
+        <v>-20952.6552922454</v>
       </c>
       <c r="C6" t="n">
-        <v>59423.23329659138</v>
+        <v>59816.77623930234</v>
       </c>
       <c r="D6" t="n">
-        <v>59423.23329659132</v>
+        <v>59816.77623930232</v>
       </c>
       <c r="E6" t="n">
-        <v>93050.83329659133</v>
+        <v>93444.37623930234</v>
       </c>
       <c r="F6" t="n">
-        <v>93050.83329659136</v>
+        <v>93444.37623930231</v>
       </c>
       <c r="G6" t="n">
-        <v>93050.83329659133</v>
+        <v>93444.37623930236</v>
       </c>
       <c r="H6" t="n">
-        <v>93050.8332965923</v>
+        <v>93444.37623930234</v>
       </c>
       <c r="I6" t="n">
-        <v>93050.83329659136</v>
+        <v>93444.37623930234</v>
       </c>
       <c r="J6" t="n">
-        <v>29994.62929659135</v>
+        <v>30384.4336401961</v>
       </c>
       <c r="K6" t="n">
-        <v>93050.83329659283</v>
+        <v>93444.37623930232</v>
       </c>
       <c r="L6" t="n">
-        <v>93050.83329659227</v>
+        <v>93444.37623930234</v>
       </c>
       <c r="M6" t="n">
-        <v>93050.83329659134</v>
+        <v>93444.37623930236</v>
       </c>
       <c r="N6" t="n">
-        <v>93050.83329659134</v>
+        <v>93444.37623930234</v>
       </c>
       <c r="O6" t="n">
-        <v>93050.83329659137</v>
+        <v>93444.37623930236</v>
       </c>
       <c r="P6" t="n">
-        <v>93050.83329659393</v>
+        <v>93444.37623930234</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34626,7 +34626,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O2" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410587</v>
       </c>
       <c r="P2" t="n">
         <v>90.5657124162131</v>
@@ -34696,16 +34696,16 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="M3" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P3" t="n">
         <v>184.4883612256069</v>
@@ -34851,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L5" t="n">
         <v>181.8947995804632</v>
@@ -34933,22 +34933,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="M6" t="n">
-        <v>161.1504669987997</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O6" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -35088,7 +35088,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L8" t="n">
         <v>181.8947995804632</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L9" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N9" t="n">
-        <v>226.3927858636066</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P9" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q9" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35325,13 +35325,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L11" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M11" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N11" t="n">
         <v>207.9338608153932</v>
@@ -35404,25 +35404,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M12" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O12" t="n">
-        <v>241</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P12" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35562,7 +35562,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L14" t="n">
         <v>181.8947995804632</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L15" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N15" t="n">
-        <v>239.9766607390412</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O15" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35799,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L17" t="n">
         <v>181.8947995804632</v>
@@ -35878,22 +35878,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L18" t="n">
-        <v>232.285965523585</v>
+        <v>34.55702612384782</v>
       </c>
       <c r="M18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P18" t="n">
-        <v>169.8811470892137</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>70.09551364982758</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439757</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,13 +36121,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>55.48829951343433</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>91.05495334897203</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="P24" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N27" t="n">
-        <v>239.9766607390412</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439973</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36832,16 +36832,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>55.48829951343436</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -36984,7 +36984,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103.9989833439752</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
@@ -37069,13 +37069,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>43.25734905099399</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -37236,7 +37236,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37306,19 +37306,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>43.25734905099399</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N36" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37458,13 +37458,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="L39" t="n">
-        <v>217.6787513871916</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37701,7 +37701,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>217.6787513871916</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N42" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37932,7 +37932,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>103.9989833440414</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L44" t="n">
         <v>181.8947995804632</v>
@@ -38011,22 +38011,22 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N45" t="n">
-        <v>43.25734905099405</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q45" t="n">
         <v>70.09551364982758</v>
